--- a/products/Salon_SNS_Booking_AI_Kit_v0.1.xlsx
+++ b/products/Salon_SNS_Booking_AI_Kit_v0.1.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" r:id="R603e9fe6448c4b6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menu Intake" sheetId="2" r:id="R1bbd4a1206354ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Calendar" sheetId="3" r:id="R973104c2e86349c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claims Safety Check" sheetId="4" r:id="R61c2acb389324030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Before After Consent" sheetId="5" r:id="Rf694229f06774457"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Booking Flow" sheetId="6" r:id="Ree6e981790574cae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Pack" sheetId="7" r:id="Rbaba4eca9e4c4571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="はじめに" sheetId="1" r:id="R5d81c2228ba04096"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="メニュー情報入力" sheetId="2" r:id="Rbb9728eaea664f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="投稿カレンダー" sheetId="3" r:id="Rcba3249115b540c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表現安全チェック" sheetId="4" r:id="R4bcccf81e39d4fae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="写真利用許可" sheetId="5" r:id="Rac048d49822f4bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="予約導線" sheetId="6" r:id="Rd23e11bf2018473d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロンプト集" sheetId="7" r:id="R27b7fd4cb6e04451"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -256,51 +256,58 @@
       </x:c>
       <x:c r="B1" s="7"/>
     </x:row>
-    <x:row r="2" ht="33" customHeight="1"/>
+    <x:row r="2" ht="33" customHeight="1">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
+    </x:row>
     <x:row r="3" ht="33" customHeight="1">
       <x:c r="A3" s="5" t="str">
         <x:v>美容室、ネイル、整体、エステなどの小規模サロンが、AIでSNS投稿・メニュー説明・予約導線を作る前に、効果表現と許可確認を整理するためのテンプレートです。</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" ht="33" customHeight="1"/>
+      <x:c r="B3"/>
+    </x:row>
+    <x:row r="4" ht="33" customHeight="1">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+    </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
-        <x:v>Step 1</x:v>
+        <x:v>手順 1</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Menu Intakeにメニューの事実、価格、所要時間を入力</x:v>
+        <x:v>メニュー情報入力にメニューの事実、価格、所要時間を入力</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>Step 2</x:v>
+        <x:v>手順 2</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>Claims Safety Checkで効果保証や医療的表現を削る</x:v>
+        <x:v>表現安全チェックで効果保証や医療的表現を削る</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
-        <x:v>Step 3</x:v>
+        <x:v>手順 3</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>Content Calendarで週5投稿の型を作る</x:v>
+        <x:v>内容 カレンダーで週5投稿の型を作る</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
-        <x:v>Step 4</x:v>
+        <x:v>手順 4</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>Before After Consentで写真利用の許可を確認</x:v>
+        <x:v>写真利用許可で写真利用の許可を確認</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
-        <x:v>Step 5</x:v>
+        <x:v>手順 5</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>Booking Flowで予約前の不安とCTAを整理</x:v>
+        <x:v>予約 導線で予約前の不安とCTAを整理</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="33" hidden="0" customHeight="1">
@@ -344,28 +351,28 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Menu</x:v>
+        <x:v>メニュー</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Price</x:v>
+        <x:v>価格</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Duration</x:v>
+        <x:v>所要時間</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Target Customer</x:v>
+        <x:v>対象顧客</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Customer Worry</x:v>
+        <x:v>顧客の不安</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Can Promise</x:v>
+        <x:v>約束できること</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Cannot Promise</x:v>
+        <x:v>約束できないこと</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -623,28 +630,28 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Post Type</x:v>
+        <x:v>投稿タイプ</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Goal</x:v>
+        <x:v>目的</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Input Needed</x:v>
+        <x:v>必要な入力</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>AI Output</x:v>
+        <x:v>AIの出力</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>CTA</x:v>
+        <x:v>行動導線</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Example Hook</x:v>
+        <x:v>書き出し例</x:v>
       </x:c>
       <x:c r="H1" s="11" t="str">
-        <x:v>Metric</x:v>
+        <x:v>指標</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -874,22 +881,22 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Risky Expression</x:v>
+        <x:v>危ない表現</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Why Risky</x:v>
+        <x:v>危ない理由</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Safer Expression</x:v>
+        <x:v>安全な表現</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Need Evidence?</x:v>
+        <x:v>根拠が必要?</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Example</x:v>
+        <x:v>例</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -903,7 +910,7 @@
         <x:v>変化を感じる方もいます</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
         <x:v>実績と個人差</x:v>
@@ -923,7 +930,7 @@
         <x:v>ケアをサポートします</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
         <x:v>医療行為との線引き</x:v>
@@ -943,7 +950,7 @@
         <x:v>似合う方向性を一緒に探します</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
         <x:v>期待値調整</x:v>
@@ -963,7 +970,7 @@
         <x:v>状態を伺いながら施術します</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
         <x:v>医療表現削除</x:v>
@@ -983,7 +990,7 @@
         <x:v>印象をすっきり見せたい方へ</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
         <x:v>写真の許可</x:v>
@@ -1003,7 +1010,7 @@
         <x:v>通いやすい価格</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
         <x:v>根拠確認</x:v>
@@ -1023,7 +1030,7 @@
         <x:v>状態を見ながら薬剤を選びます</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
         <x:v>髪の履歴確認</x:v>
@@ -1043,7 +1050,7 @@
         <x:v>ご予約が増えています</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
         <x:v>実績確認</x:v>
@@ -1063,7 +1070,7 @@
         <x:v>華やかな印象</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
         <x:v>品位</x:v>
@@ -1083,7 +1090,7 @@
         <x:v>施術内容を丁寧に説明</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
         <x:v>資格/根拠</x:v>
@@ -1103,7 +1110,7 @@
         <x:v>一度試したい方へ</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
         <x:v>個人差</x:v>
@@ -1132,25 +1139,25 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Photo Use</x:v>
+        <x:v>写真用途</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Consent Needed</x:v>
+        <x:v>許可が必要?</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Hide Face?</x:v>
+        <x:v>顔を隠す?</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Show Date?</x:v>
+        <x:v>日付を出す?</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Caption Rule</x:v>
+        <x:v>説明文ルール</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Do Not Say</x:v>
+        <x:v>言わないこと</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Record</x:v>
+        <x:v>記録</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1158,13 +1165,13 @@
         <x:v>髪型</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
         <x:v>施術内容と希望を説明</x:v>
@@ -1181,13 +1188,13 @@
         <x:v>ネイル</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
         <x:v>色やデザインを説明</x:v>
@@ -1204,13 +1211,13 @@
         <x:v>肌</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="C4" s="6" t="str">
-        <x:v>Recommended</x:v>
+        <x:v>推奨</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
         <x:v>施術内容を一般的に説明</x:v>
@@ -1227,13 +1234,13 @@
         <x:v>姿勢/整体</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>Recommended</x:v>
+        <x:v>推奨</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
         <x:v>個人差と目的を説明</x:v>
@@ -1250,13 +1257,13 @@
         <x:v>まつげ</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>Recommended</x:v>
+        <x:v>推奨</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>Optional</x:v>
+        <x:v>任意</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
         <x:v>デザインを説明</x:v>
@@ -1276,10 +1283,10 @@
         <x:v>No if no people</x:v>
       </x:c>
       <x:c r="C7" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
         <x:v>雰囲気を説明</x:v>
@@ -1296,13 +1303,13 @@
         <x:v>口コミ画面</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
-        <x:v>Yes</x:v>
+        <x:v>はい</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>No</x:v>
+        <x:v>いいえ</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
         <x:v>個人情報を隠す</x:v>
@@ -1334,25 +1341,25 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Step</x:v>
+        <x:v>手順</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Customer Question</x:v>
+        <x:v>顧客の疑問</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Page / Post Answer</x:v>
+        <x:v>ページ/投稿で答えること</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>CTA</x:v>
+        <x:v>行動導線</x:v>
       </x:c>
       <x:c r="E1" s="11" t="str">
-        <x:v>Human Check</x:v>
+        <x:v>人の確認</x:v>
       </x:c>
       <x:c r="F1" s="11" t="str">
-        <x:v>Automation OK?</x:v>
+        <x:v>自動化OK?</x:v>
       </x:c>
       <x:c r="G1" s="11" t="str">
-        <x:v>Notes</x:v>
+        <x:v>メモ</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
@@ -1372,9 +1379,9 @@
         <x:v>誇大表現</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="G2" s="6" t="str"/>
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="G2" s="6"/>
     </x:row>
     <x:row r="3" ht="33" hidden="0" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -1393,9 +1400,9 @@
         <x:v>個別判断</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>Draft only</x:v>
-      </x:c>
-      <x:c r="G3" s="6" t="str"/>
+        <x:v>下書きのみ</x:v>
+      </x:c>
+      <x:c r="G3" s="6"/>
     </x:row>
     <x:row r="4" ht="33" hidden="0" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -1414,9 +1421,9 @@
         <x:v>価格</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="str"/>
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="G4" s="6"/>
     </x:row>
     <x:row r="5" ht="33" hidden="0" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -1435,9 +1442,9 @@
         <x:v>断定表現</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>Draft only</x:v>
-      </x:c>
-      <x:c r="G5" s="6" t="str"/>
+        <x:v>下書きのみ</x:v>
+      </x:c>
+      <x:c r="G5" s="6"/>
     </x:row>
     <x:row r="6" ht="33" hidden="0" customHeight="1">
       <x:c r="A6" s="6" t="str">
@@ -1456,9 +1463,9 @@
         <x:v>空き枠</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>Draft only</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="str"/>
+        <x:v>下書きのみ</x:v>
+      </x:c>
+      <x:c r="G6" s="6"/>
     </x:row>
     <x:row r="7" ht="33" hidden="0" customHeight="1">
       <x:c r="A7" s="6" t="str">
@@ -1477,9 +1484,9 @@
         <x:v>注意事項</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="str"/>
+        <x:v>はい</x:v>
+      </x:c>
+      <x:c r="G7" s="6"/>
     </x:row>
     <x:row r="8" ht="33" hidden="0" customHeight="1">
       <x:c r="A8" s="6" t="str">
@@ -1498,9 +1505,9 @@
         <x:v>効果表現</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
-        <x:v>Draft only</x:v>
-      </x:c>
-      <x:c r="G8" s="6" t="str"/>
+        <x:v>下書きのみ</x:v>
+      </x:c>
+      <x:c r="G8" s="6"/>
     </x:row>
     <x:row r="9" ht="33" hidden="0" customHeight="1">
       <x:c r="A9" s="6" t="str">
@@ -1519,9 +1526,9 @@
         <x:v>個人差</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
-        <x:v>Draft only</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="str"/>
+        <x:v>下書きのみ</x:v>
+      </x:c>
+      <x:c r="G9" s="6"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1540,16 +1547,16 @@
   <x:sheetData>
     <x:row r="1" ht="33" hidden="0" customHeight="1">
       <x:c r="A1" s="11" t="str">
-        <x:v>Prompt</x:v>
+        <x:v>プロンプト</x:v>
       </x:c>
       <x:c r="B1" s="11" t="str">
-        <x:v>Use</x:v>
+        <x:v>用途</x:v>
       </x:c>
       <x:c r="C1" s="11" t="str">
-        <x:v>Text</x:v>
+        <x:v>本文</x:v>
       </x:c>
       <x:c r="D1" s="11" t="str">
-        <x:v>Check</x:v>
+        <x:v>確認項目</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="33" hidden="0" customHeight="1">
